--- a/sample-uploads/sample_programs.xlsx
+++ b/sample-uploads/sample_programs.xlsx
@@ -421,7 +421,7 @@
         <v>Bachelor of Science in Information Technology</v>
       </c>
       <c r="C2" t="str">
-        <v>June Arreb Danila</v>
+        <v>Kristine San Lorenzo</v>
       </c>
       <c r="D2" t="str">
         <v>Active</v>
